--- a/vault-dalarna-university/03 Analys/Samstämmighet svenska och engelska.xlsx
+++ b/vault-dalarna-university/03 Analys/Samstämmighet svenska och engelska.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Samstämmighet svenska och engel" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Samstämmighet svenska och engel'!$A$1:$E$172</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,6 +30,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="3">
@@ -55,11 +61,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -462,7 +469,4969 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>GAB3H6</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ABA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB3H6</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ABP253</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BIL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Svenska: 12 mål, engelska: 0 mål (diff 12)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABP253</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ABP254</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BIL</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Svenska: 12 mål, engelska: 0 mål (diff 12)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABP254</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>GBP32U</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIL</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Svenska: 17 mål, engelska: 0 mål (diff 17)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP32U</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>GBP32V</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BIL</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP32V</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>GBP32W</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIL</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Svenska: 16 mål, engelska: 0 mål (diff 16)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP32W</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>GBP34H</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BIL</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Svenska: 16 mål, engelska: 0 mål (diff 16)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP34H</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>GBP365</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BIL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Svenska: 11 mål, engelska: 0 mål (diff 11)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP365</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ABQ2AZ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>ABQ2B2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ABQ2B4</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>GBY2NG</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Svenska: 10 mål, engelska: 9 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2NG</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>AEN25H</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25H</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>AEN25J</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25J</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>EN2043</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Svenska: 25 mål, engelska: 0 mål (diff 25)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>GEN28Q</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Svenska: 23 mål, engelska: 1 mål (diff 22)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN28Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>GEN2BJ</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Svenska: 19 mål, engelska: 0 mål (diff 19)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>GEN2BK</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Svenska: 17 mål, engelska: 0 mål (diff 17)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BK</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>GEN2LD</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Svenska: 14 mål, engelska: 0 mål (diff 14)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2LD</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>GEN2QW</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>GEN379</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Svenska: 24 mål, engelska: 0 mål (diff 24)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>GEN37A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Svenska: 14 mål, engelska: 0 mål (diff 14)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN37A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>GEN3CM</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Svenska: 26 mål, engelska: 0 mål (diff 26)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>GEN3DG</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Svenska: 14 mål, engelska: 0 mål (diff 14)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>GEN3DK</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Svenska: 13 mål, engelska: 0 mål (diff 13)</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>FI1028</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1028</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>GFI37Z</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI37Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>GFI3BT</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BT</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>AFR24A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>AFR24B</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>GFR2YU</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>GFR3BS</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Svenska: 18 mål, engelska: 0 mål (diff 18)</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>GFR3D2</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Svenska: 44 mål, engelska: 0 mål (diff 44)</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>GFR3D3</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Svenska: 46 mål, engelska: 0 mål (diff 46)</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>GFR3HM</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Svenska: 44 mål, engelska: 0 mål (diff 44)</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>GFR3HN</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Svenska: 46 mål, engelska: 0 mål (diff 46)</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>AFT2CA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>FYS</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2CA</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>AFT2CB</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>FYS</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>GHI33T</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Svenska: 14 mål, engelska: 0 mål (diff 14)</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>GHI33V</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Svenska: 17 mål, engelska: 0 mål (diff 17)</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>GHI33W</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Svenska: 17 mål, engelska: 0 mål (diff 17)</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33W</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>GHI35A</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Svenska: 15 mål, engelska: 0 mål (diff 15)</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>GHI362</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Svenska: 11 mål, engelska: 0 mål (diff 11)</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>GHI374</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Svenska: 17 mål, engelska: 0 mål (diff 17)</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI374</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>GHI378</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Svenska: 14 mål, engelska: 0 mål (diff 14)</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI378</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>GHI3JX</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Svenska: 17 mål, engelska: 0 mål (diff 17)</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI3JX</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>GIH334</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH334</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>GIH35T</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Svenska: 2 mål, engelska: 0 mål (diff 2)</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35T</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>GIH35U</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35U</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>GIH35W</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35W</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>GIH37R</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Svenska: 15 mål, engelska: 1 mål (diff 14)</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>GIH37S</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Svenska: 19 mål, engelska: 0 mål (diff 19)</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37S</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>GIH38Y</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 5 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH38Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>GIH39C</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39C</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>GIH3AN</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Svenska: 23 mål, engelska: 1 mål (diff 22)</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AN</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>GIH3AP</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Svenska: 23 mål, engelska: 1 mål (diff 22)</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>GIH3AQ</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>GIH3C2</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>GIK23M</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 5 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK23M</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>GIK2KM</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Svenska: 10 mål, engelska: 9 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2KM</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>AKI25K</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Svenska: 12 mål, engelska: 1 mål (diff 11)</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>GKI2W3</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Svenska: 27 mål, engelska: 1 mål (diff 26)</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>AMC2BG</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>GMC37E</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Svenska: 1 mål, engelska: 0 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>AMD238</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>MDI</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Svenska: 17 mål, engelska: 0 mål (diff 17)</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>AMD239</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>MDI</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Svenska: 17 mål, engelska: 0 mål (diff 17)</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>GMD2AR</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>MDI</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Svenska: 28 mål, engelska: 0 mål (diff 28)</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2AR</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>GMD2GG</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>MDI</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Svenska: 24 mål, engelska: 1 mål (diff 23)</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>GMD2H2</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>MDI</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Svenska: 9 mål, engelska: 8 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>GMD2MH</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>MDI</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>GMD2TV</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>MDI</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Svenska: 32 mål, engelska: 0 mål (diff 32)</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2TV</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>GMT34R</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Svenska: 10 mål, engelska: 11 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>MT1033</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Svenska: 1 mål, engelska: 0 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1033</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>GNA3B8</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 6 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>NA2001</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 3 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>NA3001</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Svenska: 10 mål, engelska: 9 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>NA3005</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 6 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3005</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>NA3007</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 9 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>GNV367</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Svenska: 16 mål, engelska: 0 mål (diff 16)</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>APG244</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG244</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>APG245</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG245</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>APG246</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG246</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>APG247</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>APG24E</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>APG28R</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28R</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>APG2BC</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Svenska: 12 mål, engelska: 0 mål (diff 12)</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>APG2C7</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C7</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>GPG22J</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22J</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>GPG2E7</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E7</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>GPG2LZ</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>GPG2QP</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Svenska: 15 mål, engelska: 14 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>GPG2RH</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Svenska: 15 mål, engelska: 14 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>GPG2RR</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Svenska: 13 mål, engelska: 12 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>GPG2RS</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Svenska: 16 mål, engelska: 15 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>GPG2S7</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Svenska: 13 mål, engelska: 12 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>GPG2S8</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Svenska: 16 mål, engelska: 15 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>GPG2YG</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YG</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>GPG2Z3</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>GPG326</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG326</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>GPG3AB</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CF</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Svenska: 13 mål, engelska: 0 mål (diff 13)</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CG</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Svenska: 13 mål, engelska: 0 mål (diff 13)</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CH</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Svenska: 11 mål, engelska: 0 mål (diff 11)</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CJ</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Svenska: 11 mål, engelska: 0 mål (diff 11)</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CL</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Svenska: 27 mål, engelska: 0 mål (diff 27)</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>GPG3EU</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Svenska: 15 mål, engelska: 0 mål (diff 15)</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>GPG3EV</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Svenska: 13 mål, engelska: 0 mål (diff 13)</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>GPG3FV</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>PG3024</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>PG3025</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>PG3041</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>GPR3GM</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Svenska: 12 mål, engelska: 11 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GM</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>GPR3GN</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Svenska: 11 mål, engelska: 10 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>GPR3GP</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Svenska: 16 mål, engelska: 15 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GP</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>GRK2P3</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>GRK2Q4</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>GRK2Q5</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Svenska: 11 mål, engelska: 0 mål (diff 11)</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>GRK2TW</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>GRK2TY</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>GRK2TZ</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>GRK324</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Svenska: 22 mål, engelska: 0 mål (diff 22)</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>GRK32C</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK32C</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>GRV3BF</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>ASA266</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA266</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>GSA27Y</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA27Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>GSA2AF</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Svenska: 14 mål, engelska: 0 mål (diff 14)</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>GSA2BV</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Svenska: 11 mål, engelska: 0 mål (diff 11)</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>GSA2NA</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>GSA2RE</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2RE</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>GSA3HA</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Svenska: 12 mål, engelska: 0 mål (diff 12)</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3HA</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>GSO2UA</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Svenska: 16 mål, engelska: 0 mål (diff 16)</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>GSO2XU</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Svenska: 19 mål, engelska: 0 mål (diff 19)</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>GSO2XV</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Svenska: 13 mål, engelska: 0 mål (diff 13)</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>SO1030</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>ASP25D</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>ASP25E</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>GSP28C</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Svenska: 12 mål, engelska: 1 mål (diff 11)</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP28C</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>GSP2FQ</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Svenska: 33 mål, engelska: 0 mål (diff 33)</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>GSP2FR</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>GSP2W8</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Svenska: 31 mål, engelska: 0 mål (diff 31)</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>GSQ33M</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 4 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33M</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>ASR29V</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Svenska: 13 mål, engelska: 12 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>GSS2FK</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Svenska: 20 mål, engelska: 0 mål (diff 20)</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BL</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Svenska: 15 mål, engelska: 0 mål (diff 15)</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BN</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Svenska: 20 mål, engelska: 0 mål (diff 20)</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>GSS3C7</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Svenska: 15 mål, engelska: 0 mål (diff 15)</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>GSS3H8</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Svenska: 20 mål, engelska: 0 mål (diff 20)</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>GSS3HB</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Svenska: 20 mål, engelska: 0 mål (diff 20)</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>GSS3HG</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Svenska: 16 mål, engelska: 0 mål (diff 16)</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>GSS3HJ</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Svenska: 20 mål, engelska: 0 mål (diff 20)</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>SS2007</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>ST1013</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>STA</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ST1013</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZU</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Svenska: 23 mål, engelska: 0 mål (diff 23)</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZV</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Svenska: 23 mål, engelska: 0 mål (diff 23)</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZW</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Svenska: 25 mål, engelska: 0 mål (diff 25)</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZX</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Svenska: 25 mål, engelska: 0 mål (diff 25)</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DD</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Svenska: 20 mål, engelska: 0 mål (diff 20)</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DE</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Svenska: 23 mål, engelska: 0 mål (diff 23)</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DF</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Svenska: 23 mål, engelska: 0 mål (diff 23)</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>ATY255</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>ATY256</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>GTY2N5</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Svenska: 22 mål, engelska: 0 mål (diff 22)</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>GTY2SW</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>GTY3CT</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Svenska: 36 mål, engelska: 0 mål (diff 36)</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>GTY3CU</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Svenska: 34 mål, engelska: 0 mål (diff 34)</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>GTY3J9</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Svenska: 37 mål, engelska: 0 mål (diff 37)</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>GTY3JB</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Svenska: 15 mål, engelska: 0 mål (diff 15)</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>TY1038</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1038</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>TY1066</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>TY1067</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1067</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>AMI23A</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 4 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:E172"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId342"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>